--- a/docs/Sales/AgriX_Sablon_ponude.xlsx
+++ b/docs/Sales/AgriX_Sablon_ponude.xlsx
@@ -725,6 +725,7 @@
       <c r="E4" s="39" t="n"/>
       <c r="F4" s="39" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="33">
       <c r="A6" s="40" t="inlineStr">
         <is>
@@ -787,6 +788,7 @@
       <c r="E11" s="43" t="n"/>
       <c r="F11" s="43" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="40" t="inlineStr">
         <is>
@@ -1062,6 +1064,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="19.7" customHeight="1" s="33">
       <c r="A26" s="53" t="n"/>
       <c r="B26" s="54" t="inlineStr">
@@ -1096,6 +1099,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="33">
       <c r="A29" s="40" t="inlineStr">
         <is>
@@ -1218,6 +1222,7 @@
       </c>
       <c r="F34" s="53" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="33">
       <c r="A36" s="40" t="inlineStr">
         <is>
@@ -1267,6 +1272,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="33">
       <c r="A44" s="40" t="inlineStr">
         <is>
@@ -1309,6 +1315,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="33">
       <c r="B52" s="40" t="inlineStr">
         <is>
@@ -1316,6 +1324,8 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55" ht="15" customHeight="1" s="33">
       <c r="B55" s="41" t="inlineStr">
         <is>
@@ -1705,7 +1715,7 @@
     <row r="22">
       <c r="A22" s="50" t="inlineStr">
         <is>
-          <t>Savetnik — standalone osnovica</t>
+          <t>Savetnik — standalone osnovica [u pripremi]</t>
         </is>
       </c>
       <c r="B22" s="48" t="n">
@@ -1713,14 +1723,14 @@
       </c>
       <c r="C22" s="49" t="inlineStr">
         <is>
-          <t>odluka 419 — do 10 gazdinstava</t>
+          <t>odluka 419 — do 10 gazdinstava — U PRIPREMI (odluka 423): ne uvrstavati u ponudu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="inlineStr">
         <is>
-          <t>Savetnik — standalone po gazdinstvu</t>
+          <t>Savetnik — standalone po gazdinstvu [u pripremi]</t>
         </is>
       </c>
       <c r="B23" s="48" t="n">
@@ -1728,14 +1738,14 @@
       </c>
       <c r="C23" s="49" t="inlineStr">
         <is>
-          <t>odluka 419 — preko 10</t>
+          <t>odluka 419 — preko 10 — U PRIPREMI (odluka 423): ne uvrstavati u ponudu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="inlineStr">
         <is>
-          <t>Savetnik — Enterprise osnovica</t>
+          <t>Savetnik — Enterprise osnovica [u pripremi]</t>
         </is>
       </c>
       <c r="B24" s="48" t="n">
@@ -1743,14 +1753,14 @@
       </c>
       <c r="C24" s="49" t="inlineStr">
         <is>
-          <t>odluka 419 — uz aktivan Enterprise ugovor</t>
+          <t>odluka 419 — uz aktivan Enterprise ugovor — U PRIPREMI (odluka 423): ne uvrstavati u ponudu</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="inlineStr">
         <is>
-          <t>Savetnik — Enterprise po gazdinstvu</t>
+          <t>Savetnik — Enterprise po gazdinstvu [u pripremi]</t>
         </is>
       </c>
       <c r="B25" s="48" t="n">
@@ -1758,7 +1768,7 @@
       </c>
       <c r="C25" s="49" t="inlineStr">
         <is>
-          <t>odluka 419 — preko 10</t>
+          <t>odluka 419 — preko 10 — U PRIPREMI (odluka 423): ne uvrstavati u ponudu</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1898,8 @@
     <row r="19" ht="15" customHeight="1" s="33">
       <c r="A19" s="63" t="inlineStr">
         <is>
-          <t>·  Dispatch se nudi samo uz Mobile paket (odluka 293). Desktop all-in NE sadrži Dispatch (odluka 415).</t>
+          <t>·  Dispatch se nudi samo uz Mobile paket (odluka 293). Desktop all-in NE sadrži Dispatch (odluka 415).
+·  AgriX Savetnik je u pripremi (odluka 423) — ne uvrstava se u ponudu dok proizvod ne bude stabilan.</t>
         </is>
       </c>
     </row>

--- a/docs/Sales/AgriX_Sablon_ponude.xlsx
+++ b/docs/Sales/AgriX_Sablon_ponude.xlsx
@@ -220,7 +220,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -411,6 +411,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -665,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
@@ -725,7 +728,6 @@
       <c r="E4" s="39" t="n"/>
       <c r="F4" s="39" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="33">
       <c r="A6" s="40" t="inlineStr">
         <is>
@@ -788,7 +790,6 @@
       <c r="E11" s="43" t="n"/>
       <c r="F11" s="43" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="40" t="inlineStr">
         <is>
@@ -904,7 +905,7 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>po proizvodnom pogonu; dodatni pogon 200 € (412, 421)</t>
+          <t>0 = ne uzima, 1 = prvi proizvodni pogon; dodatne pogone unesi u red 10 (412, 421)</t>
         </is>
       </c>
     </row>
@@ -1064,287 +1065,370 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>Modul Hladnjača / Proizvodnja — dodatni pogoni</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="65">
+        <f>INDEX(Cenovnik!$B$5:$B$25,MATCH("Modul Hladnjača / Proizvodnja — dodatni pogon",Cenovnik!$A$5:$A$25,0))</f>
+        <v/>
+      </c>
+      <c r="E25" s="48">
+        <f>C25*D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>broj pogona PREKO prvog; prvi je u redu 3 (odluke 412, 413, 421)</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="19.7" customHeight="1" s="33">
-      <c r="A26" s="53" t="n"/>
-      <c r="B26" s="54" t="inlineStr">
-        <is>
-          <t>UKUPNO GODIŠNJE</t>
-        </is>
-      </c>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
-      <c r="E26" s="55">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-      <c r="F26" s="53" t="n"/>
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>Gazdinstvo Basic — nalozi kooperanata</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="65">
+        <f>INDEX(Cenovnik!$B$5:$B$25,MATCH("Gazdinstvo Basic — kanalska cena",Cenovnik!$A$5:$A$25,0))</f>
+        <v/>
+      </c>
+      <c r="E26" s="48">
+        <f>C26*D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>kanalska cena; prvih 50 naloga partner dobija bez naknade (161)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="33">
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>Kurs za informativni preračun</t>
-        </is>
-      </c>
-      <c r="C27" s="56" t="n">
-        <v>117</v>
-      </c>
-      <c r="E27" s="57">
-        <f>E26*C27</f>
-        <v/>
-      </c>
-      <c r="F27" s="52" t="inlineStr">
-        <is>
-          <t>informativno; plaća se po kursu na dan uplate</t>
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>Dodatna instanca — 50 % od liste cena stavki koje koristi</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="48">
+        <f>C27*D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>u Količinu unesi zbir liste cena stavki koje ta instanca dodatno koristi, u EUR (413)</t>
         </is>
       </c>
     </row>
     <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="33">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="53" t="n"/>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>UKUPNO GODIŠNJE</t>
+        </is>
+      </c>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
+      <c r="E29" s="55">
+        <f>SUM(E15:E27)</f>
+        <v/>
+      </c>
+      <c r="F29" s="53" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="33">
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>Kurs za informativni preračun</t>
+        </is>
+      </c>
+      <c r="C30" s="56" t="n">
+        <v>117</v>
+      </c>
+      <c r="E30" s="57">
+        <f>E29*C30</f>
+        <v/>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>informativno; plaća se po kursu na dan uplate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="33"/>
+    <row r="32" ht="15" customHeight="1" s="33">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>JEDNOKRATNE USLUGE</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="33">
-      <c r="A30" s="58" t="n"/>
-      <c r="B30" s="58" t="inlineStr">
+    <row r="33" ht="15" customHeight="1" s="33">
+      <c r="A33" s="58" t="n"/>
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>Usluga</t>
         </is>
       </c>
-      <c r="C30" s="58" t="inlineStr">
+      <c r="C33" s="58" t="inlineStr">
         <is>
           <t>Sati</t>
         </is>
       </c>
-      <c r="D30" s="58" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>Cena</t>
         </is>
       </c>
-      <c r="E30" s="58" t="inlineStr">
+      <c r="E33" s="58" t="inlineStr">
         <is>
           <t>Iznos</t>
         </is>
       </c>
-      <c r="F30" s="58" t="inlineStr">
+      <c r="F33" s="58" t="inlineStr">
         <is>
           <t>Napomena</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="33">
-      <c r="A31" s="59" t="n"/>
-      <c r="B31" s="50" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="33">
+      <c r="A34" s="59" t="n"/>
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>Složena migracija podataka</t>
         </is>
       </c>
-      <c r="C31" s="51" t="n">
+      <c r="C34" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D34" s="48">
         <f>INDEX(Cenovnik!$B$5:$B$25,MATCH("Satnica — razvojna",Cenovnik!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="E31" s="48">
-        <f>C31*D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="49" t="inlineStr">
+      <c r="E34" s="48">
+        <f>C34*D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
         <is>
           <t>razvojna satnica 50 €/h (409)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="33">
-      <c r="A32" s="59" t="n"/>
-      <c r="B32" s="50" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="59" t="n"/>
+      <c r="B35" s="50" t="inlineStr">
         <is>
           <t>Dodatna obuka preko 5 sati</t>
         </is>
       </c>
-      <c r="C32" s="51" t="n">
+      <c r="C35" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="48">
+      <c r="D35" s="48">
         <f>INDEX(Cenovnik!$B$5:$B$25,MATCH("Satnica — implementaciona",Cenovnik!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="E32" s="48">
-        <f>C32*D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="49" t="inlineStr">
+      <c r="E35" s="48">
+        <f>C35*D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
         <is>
           <t>implementaciona satnica 30 €/h (409); 5 sati je ukljuceno u onboarding</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="33">
-      <c r="A33" s="59" t="n"/>
-      <c r="B33" s="50" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="33">
+      <c r="A36" s="59" t="n"/>
+      <c r="B36" s="50" t="inlineStr">
         <is>
           <t>Razvoj po zahtevu</t>
         </is>
       </c>
-      <c r="C33" s="51" t="n">
+      <c r="C36" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="48">
+      <c r="D36" s="48">
         <f>INDEX(Cenovnik!$B$5:$B$25,MATCH("Satnica — razvojna",Cenovnik!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="E33" s="48">
-        <f>C33*D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="49" t="inlineStr">
+      <c r="E36" s="48">
+        <f>C36*D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
         <is>
           <t>razvojna satnica 50 €/h (409); uz procenu i maksimalni budzet</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="33">
-      <c r="A34" s="53" t="n"/>
-      <c r="B34" s="54" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="33">
+      <c r="A37" s="53" t="n"/>
+      <c r="B37" s="54" t="inlineStr">
         <is>
           <t>Ukupno jednokratno</t>
         </is>
       </c>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
-      <c r="E34" s="60">
-        <f>SUM(E31:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="53" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36" ht="15" customHeight="1" s="33">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="60">
+        <f>SUM(E34:E36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="53" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="33"/>
+    <row r="39" ht="15" customHeight="1" s="33">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>UKLJUČENO U GODIŠNJU NAKNADU</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="33">
-      <c r="B37" s="41" t="inlineStr">
-        <is>
-          <t>·  Instalacija sistema i povezivanje svih komponenti</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="33">
-      <c r="B38" s="41" t="inlineStr">
-        <is>
-          <t>·  Implementaciona obuka u trajanju do 5 sati</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="33">
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>·  Otklanjanje grešaka, bezbednosne ispravke i nove verzije</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="33">
       <c r="B40" s="41" t="inlineStr">
         <is>
-          <t>·  Prilagođavanje izmenama propisa — bez naplate</t>
+          <t>·  Instalacija sistema i povezivanje svih komponenti</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="33">
       <c r="B41" s="41" t="inlineStr">
         <is>
-          <t>·  Podrška telefonom, mejlom i daljinskom dijagnostikom, radnim danima 08–16</t>
+          <t>·  Implementaciona obuka u trajanju do 5 sati</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="33">
       <c r="B42" s="41" t="inlineStr">
         <is>
-          <t>·  Vikend podrška za kritične incidente tokom sezone, 1. jun — 30. novembar</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
+          <t>·  Otklanjanje grešaka, bezbednosne ispravke i nove verzije</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>·  Prilagođavanje izmenama propisa — bez naplate</t>
+        </is>
+      </c>
+    </row>
     <row r="44" ht="15" customHeight="1" s="33">
-      <c r="A44" s="40" t="inlineStr">
-        <is>
-          <t>USLOVI</t>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>·  Podrška telefonom, mejlom i daljinskom dijagnostikom, radnim danima 08–16</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="33">
       <c r="B45" s="41" t="inlineStr">
         <is>
-          <t>·  Cene su iskazane u evrima, bez PDV-a, na godišnjem nivou.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="33">
-      <c r="B46" s="41" t="inlineStr">
-        <is>
-          <t>·  Plaćanje se vrši u dinarima, po srednjem kursu NBS na dan uplate.</t>
-        </is>
-      </c>
-    </row>
+          <t>·  Vikend podrška za kritične incidente tokom sezone, 1. jun — 30. novembar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="33"/>
     <row r="47" ht="15" customHeight="1" s="33">
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>·  Ugovor se zaključuje na 12 meseci; naknada se plaća pre aktivacije.</t>
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>USLOVI</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="33">
       <c r="B48" s="41" t="inlineStr">
         <is>
-          <t>·  Ponuda važi 30 dana od datuma izdavanja.</t>
+          <t>·  Cene su iskazane u evrima, bez PDV-a, na godišnjem nivou.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="33">
       <c r="B49" s="41" t="inlineStr">
         <is>
+          <t>·  Plaćanje se vrši u dinarima, po srednjem kursu NBS na dan uplate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>·  Ugovor se zaključuje na 12 meseci; naknada se plaća pre aktivacije.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>·  Ponuda važi 30 dana od datuma izdavanja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="33">
+      <c r="B52" s="41" t="inlineStr">
+        <is>
           <t>·  AgriX vodi operativni tok firme i povezuje se sa knjigovodstvom, ali ne zamenjuje računovodstveni ERP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52" ht="15" customHeight="1" s="33">
-      <c r="B52" s="40" t="inlineStr">
-        <is>
-          <t>Sledeći korak: potvrda obima i dogovor termina uvođenja pre početka sezone.</t>
         </is>
       </c>
     </row>
     <row r="53"/>
     <row r="54"/>
     <row r="55" ht="15" customHeight="1" s="33">
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>Sledeći korak: potvrda obima i dogovor termina uvođenja pre početka sezone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="33"/>
+    <row r="57"/>
+    <row r="58">
+      <c r="B58" s="41" t="inlineStr">
         <is>
           <t>_______________________</t>
         </is>
       </c>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="E58" s="41" t="inlineStr">
         <is>
           <t>_______________________</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="33">
-      <c r="B56" s="52" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="52" t="inlineStr">
         <is>
           <t>za AgriX</t>
         </is>
       </c>
-      <c r="E56" s="52" t="inlineStr">
+      <c r="E59" s="52" t="inlineStr">
         <is>
           <t>za Korisnika</t>
         </is>
@@ -1798,7 +1882,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="33">
       <c r="A3" s="63" t="n"/>
     </row>
